--- a/translation/review/000scriptAKYO_0035A.xlsx
+++ b/translation/review/000scriptAKYO_0035A.xlsx
@@ -31,7 +31,7 @@
     <t>The opponents join under similar conditions. Even if I'm the bait or whatever, it's obvious that a unskillful player like me can only be a liability.</t>
   </si>
   <si>
-    <t>Los oponentes se unen en condiciones similares. Incluso si soy el cebo o lo que sea, es obvio que un jugador sin habilidad como yo solo puede ser una desventaja.</t>
+    <t>Los oponentes se unen en condiciones similares.＿Incluso si soy el cebo o lo que sea, es obvio[que un jugador sin habilidad como yo solo＿puede ser una desventaja.]</t>
   </si>
   <si>
     <t>Kirino</t>
@@ -70,19 +70,19 @@
     <t>There is a reason for you to take part in the tournament, Kyousuke-shi. Cannon fodder or bait, these are just excuses!</t>
   </si>
   <si>
-    <t>Hay una razón para que participes en el torneo, Kyousuke-shi. ¡Carne de cañón o cebo, esas son solo excusas!</t>
+    <t>Hay una razón para que participes en el torneo,＿Kyousuke-shi. ¡Carne de cañón o cebo, esas＿son solo excusas!</t>
   </si>
   <si>
     <t>Huhu, that's because Kiririn-shi and Kuroneko-shi aren't being honest.</t>
   </si>
   <si>
-    <t>Juju, es porque Kiririn-shi y Kuroneko-shi no están siendo sinceras.</t>
+    <t>Juju, es porque Kiririn-shi y Kuroneko-shi no＿están siendo sinceras.</t>
   </si>
   <si>
     <t>...H-Hmph, you could have said that from the start. In that case I would've...</t>
   </si>
   <si>
-    <t>...H-Hmph, podrías haber dicho eso desde el principio. En ese caso yo habría...</t>
+    <t>...H-Hmph, podrías haber dicho eso desde el＿principio. En ese caso yo habría...</t>
   </si>
   <si>
     <t>My, my... Kyousuke-shi really is dense.</t>
@@ -106,49 +106,49 @@
     <t>After I finally gave up, Kirino and the rest immediately started training at Siscaly.</t>
   </si>
   <si>
-    <t>Después de que finalmente me rendí, Kirino y las demás comenzaron de inmediato a entrenar en Siscaly.</t>
+    <t>Después de que finalmente me rendí, Kirino y las＿demás comenzaron de inmediato a entrenar en＿Siscaly.</t>
   </si>
   <si>
     <t>Kuroneko's expression completely changed the moment the game started.</t>
   </si>
   <si>
-    <t>La expresión de Kuroneko cambió por completo en el momento en que empezó el juego.</t>
+    <t>La expresión de Kuroneko cambió por completo＿en el momento en que empezó el juego.</t>
   </si>
   <si>
     <t>She used the controller with such speed that I couldn't even see her fingers moving.</t>
   </si>
   <si>
-    <t>Usaba el control con tanta velocidad que ni siquiera podía ver sus dedos moverse.</t>
+    <t>Usaba el control con tanta velocidad que ni＿siquiera podía ver sus dedos moverse.</t>
   </si>
   <si>
     <t>Kuroneko's character, "Alicia Blackcat", danced like butterflies as she went on the offensive against Kirino's character, "Tenjouin Mikoto".</t>
   </si>
   <si>
-    <t>El personaje de Kuroneko, «Alicia Blackcat», bailaba como mariposas mientras atacaba al personaje de Kirino, «Tenjouin Mikoto».</t>
+    <t>El personaje de Kuroneko, «Alicia Blackcat»,＿bailaba como mariposas mientras atacaba al＿personaje de Kirino, «Tenjouin Mikoto».</t>
   </si>
   <si>
     <t>Wow... It's completely different when you see an expert playing.</t>
   </si>
   <si>
-    <t>Wow... Es completamente diferente cuando ves jugar a un experto.</t>
+    <t>Wow... Es completamente diferente cuando ves＿jugar a un experto.</t>
   </si>
   <si>
     <t>Although you pretend to be skillful, in truth you do not even measure up to me.</t>
   </si>
   <si>
-    <t>Aunque pretendes ser hábil, en verdad ni siquiera estás a mi altura.</t>
+    <t>Aunque pretendes ser hábil, en verdad ni＿siquiera estás a mi altura.</t>
   </si>
   <si>
     <t>Ooh! As expected of the 【National Level】 Kuroneko-shi!</t>
   </si>
   <si>
-    <t>¡Ooh! ¡Como era de esperar de Kuroneko-shi de 【Nivel Nacional】!</t>
+    <t>¡Ooh! ¡Como era de esperar de Kuroneko-shi de＿【Nivel Nacional】!</t>
   </si>
   <si>
     <t>You're just a malicious and delusional girl. As always, you're "only skilled at video games".</t>
   </si>
   <si>
-    <t>Solo eres una chica maliciosa y delirante. Como siempre, «solo eres buena en los videojuegos».</t>
+    <t>Solo eres una chica maliciosa y delirante. Como＿siempre, «solo eres buena en los videojuegos».</t>
   </si>
   <si>
     <t>She especially emphasized the word "only".</t>
@@ -160,19 +160,19 @@
     <t>However, Kuroneko's moves are really good...</t>
   </si>
   <si>
-    <t>Sin embargo, los movimientos de Kuroneko son realmente buenos...</t>
+    <t>Sin embargo, los movimientos de Kuroneko son＿realmente buenos...</t>
   </si>
   <si>
     <t>Aren't we extremely lucky to have her as an ally?</t>
   </si>
   <si>
-    <t>¿No somos extremadamente afortunados de tenerla como aliada?</t>
+    <t>¿No somos extremadamente afortunados de＿tenerla como aliada?</t>
   </si>
   <si>
     <t>Do you not realize? Your moves, I know them like the back of my hand.</t>
   </si>
   <si>
-    <t>¿No te das cuenta? Conozco tus movimientos como la palma de mi mano.</t>
+    <t>¿No te das cuenta? Conozco tus movimientos＿como la palma de mi mano.</t>
   </si>
   <si>
     <t>Ugh...</t>
@@ -223,7 +223,7 @@
     <t>Ah, ah. Kirino, she's glaring intensely at Kuroneko.</t>
   </si>
   <si>
-    <t>Ah, ah. Kirino está fulminando con la mirada a Kuroneko.</t>
+    <t>Ah, ah. Kirino está fulminando con la mirada a＿Kuroneko.</t>
   </si>
   <si>
     <t>Kirino, I know that feeling well-</t>
@@ -253,7 +253,7 @@
     <t>It's because you were dilly-dallying, it made me lose focus!</t>
   </si>
   <si>
-    <t>¡Es porque estabas dando vueltas, eso me hizo perder la concentración!</t>
+    <t>¡Es porque estabas dando vueltas, eso me hizo＿perder la concentración!</t>
   </si>
   <si>
     <t>T-This is my fault?!</t>
@@ -331,13 +331,13 @@
     <t>I must decline. Please do not interrupt me during a duel.</t>
   </si>
   <si>
-    <t>Debo declinar. Por favor, no me interrumpas durante un duelo.</t>
+    <t>Debo declinar. Por favor, no me interrumpas＿durante un duelo.</t>
   </si>
   <si>
     <t>You two... It's merely a game, you're overreacting!</t>
   </si>
   <si>
-    <t>Ustedes dos... Es solo un juego, ¡están exagerando!</t>
+    <t>Ustedes dos... Es solo un juego, ¡están＿exagerando!</t>
   </si>
   <si>
     <t>...Merely?</t>
@@ -361,19 +361,19 @@
     <t>What do you mean it's merely a game? Do you still not understand?</t>
   </si>
   <si>
-    <t>¿Qué quieres decir con que es solo un juego? ¿Todavía no entiendes?</t>
+    <t>¿Qué quieres decir con que es solo un juego?＿¿Todavía no entiendes?</t>
   </si>
   <si>
     <t>This is a game, yet not a game. Have you still not realized that?</t>
   </si>
   <si>
-    <t>Esto es un juego, y a la vez no lo es. ¿Todavía no te has dado cuenta?</t>
+    <t>Esto es un juego, y a la vez no lo es. ¿Todavía＿no te has dado cuenta?</t>
   </si>
   <si>
     <t>Well, well. The two of you don't need to be so fired up...</t>
   </si>
   <si>
-    <t>Bueno, bueno. Ustedes dos no necesitan estar tan acaloradas...</t>
+    <t>Bueno, bueno. Ustedes dos no necesitan estar＿tan acaloradas...</t>
   </si>
   <si>
     <t>Hah!?</t>
@@ -391,7 +391,7 @@
     <t>Anyway, what Kiririn-shi needs is to "calm down"!</t>
   </si>
   <si>
-    <t>De todos modos, ¡lo que Kiririn-shi necesita es «calmarse»!</t>
+    <t>De todos modos, ¡lo que Kiririn-shi necesita es＿«calmarse»!</t>
   </si>
   <si>
     <t>I know that, even if you hadn't said it.</t>
@@ -403,25 +403,25 @@
     <t>After that, we changed our pairings many times and trained hard, but there was no breakthrough.</t>
   </si>
   <si>
-    <t>Después de eso, cambiamos nuestras parejas muchas veces y entrenamos duro, pero no hubo avance.</t>
+    <t>Después de eso, cambiamos nuestras parejas＿muchas veces y entrenamos duro, pero no hubo＿avance.</t>
   </si>
   <si>
     <t>Facing the national-level Kuroneko is out of question, but I still have trouble reading Kirino and Saori's moves.</t>
   </si>
   <si>
-    <t>Enfrentar a la Kuroneko de nivel nacional está fuera de cuestión, pero aún tengo problemas para leer los movimientos de Kirino y Saori.</t>
+    <t>Enfrentar a la Kuroneko de nivel nacional está＿fuera de cuestión, pero aún tengo problemas＿para leer los movimientos de Kirino y Saori.</t>
   </si>
   <si>
     <t>After being humiliated for dozens of rounds, this time it's Kirino &amp; Kuroneko vs Saori &amp; myself.</t>
   </si>
   <si>
-    <t>Después de ser humillado durante docenas de rondas, esta vez es Kirino y Kuroneko contra Saori y yo.</t>
+    <t>Después de ser humillado durante docenas de＿rondas, esta vez es Kirino y Kuroneko contra＿Saori y yo.</t>
   </si>
   <si>
     <t>No matter how you think about it, we should have no chance to win... However-</t>
   </si>
   <si>
-    <t>No importa cómo lo pienses, no deberíamos tener oportunidad de ganar... Sin embargo-</t>
+    <t>No importa cómo lo pienses, no deberíamos tener＿oportunidad de ganar... Sin embargo-</t>
   </si>
   <si>
     <t>W-Wait! What are you doing?</t>
@@ -445,7 +445,7 @@
     <t>I don't need your help. I will maintain control over the battlefield by myself.</t>
   </si>
   <si>
-    <t>No necesito tu ayuda. Mantendré el control del campo de batalla yo sola.</t>
+    <t>No necesito tu ayuda. Mantendré el control del＿campo de batalla yo sola.</t>
   </si>
   <si>
     <t>Hah?!</t>
@@ -454,7 +454,7 @@
     <t>Frankly speaking, you're nothing but a nuisance.</t>
   </si>
   <si>
-    <t>Hablando con franqueza, no eres más que una molestia.</t>
+    <t>Hablando con franqueza, no eres más que una＿molestia.</t>
   </si>
   <si>
     <t>What's with that excuse!</t>
@@ -466,7 +466,7 @@
     <t>Then how about having a 3-on-1 battle? I can release my sealed powers if there's nobody in my way.</t>
   </si>
   <si>
-    <t>Entonces, ¿qué tal una batalla de 3 contra 1? Puedo liberar mis poderes sellados si no hay nadie en mi camino.</t>
+    <t>Entonces, ¿qué tal una batalla de 3 contra 1?＿Puedo liberar mis poderes sellados si no hay＿nadie en mi camino.</t>
   </si>
   <si>
     <t>...You really piss me off.</t>
@@ -484,7 +484,7 @@
     <t>In the end, they forgot about the controllers and the quarreling started.</t>
   </si>
   <si>
-    <t>Al final, se olvidaron de los controles y empezó la pelea.</t>
+    <t>Al final, se olvidaron de los controles y empezó la＿pelea.</t>
   </si>
   <si>
     <t>With the two of them like that-</t>
@@ -502,25 +502,25 @@
     <t>The uncontrolled characters are then swiftly taken care of.</t>
   </si>
   <si>
-    <t>Los personajes descontrolados son eliminados rápidamente.</t>
+    <t>Los personajes descontrolados son eliminados＿rápidamente.</t>
   </si>
   <si>
     <t>This memorable first victory, was brought to us by our two aces's ugly infighting.</t>
   </si>
   <si>
-    <t>Esta memorable primera victoria nos la trajo la fea pelea interna de nuestras dos ases.</t>
+    <t>Esta memorable primera victoria nos la trajo la fea＿pelea interna de nuestras dos ases.</t>
   </si>
   <si>
     <t>You two... At least be friendly when you play together!</t>
   </si>
   <si>
-    <t>Ustedes dos... ¡Al menos sean amables cuando jueguen juntas!</t>
+    <t>Ustedes dos... ¡Al menos sean amables cuando＿jueguen juntas!</t>
   </si>
   <si>
     <t>Although they socialize without reservation when playing games, when it comes to being on good terms outside of that...</t>
   </si>
   <si>
-    <t>Aunque socializan sin reservas cuando juegan, cuando se trata de llevarse bien fuera de eso...</t>
+    <t>Aunque socializan sin reservas cuando juegan,＿cuando se trata de llevarse bien fuera de eso...</t>
   </si>
   <si>
     <t>There's something more to it, huh?</t>
